--- a/data/trans_dic/P2A_ner_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,12</t>
+          <t>1,95; 6,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 6,22</t>
+          <t>1,82; 5,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,96; 11,05</t>
+          <t>4,89; 11,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 6,66</t>
+          <t>1,85; 6,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 10,16</t>
+          <t>3,6; 10,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 9,7</t>
+          <t>3,55; 9,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,89; 20,82</t>
+          <t>12,1; 21,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,88</t>
+          <t>1,38; 3,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 7,18</t>
+          <t>3,48; 7,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,4; 7,1</t>
+          <t>3,38; 6,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,18; 14,9</t>
+          <t>9,24; 15,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,68</t>
+          <t>1,85; 4,63</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,0</t>
+          <t>2,3; 5,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,37</t>
+          <t>1,57; 5,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,26</t>
+          <t>1,9; 5,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,08</t>
+          <t>1,22; 4,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 8,11</t>
+          <t>3,67; 7,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 8,34</t>
+          <t>4,1; 8,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,61; 13,09</t>
+          <t>7,67; 13,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,45; 7,98</t>
+          <t>4,48; 7,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 6,19</t>
+          <t>3,54; 6,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,12</t>
+          <t>3,29; 6,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,34; 8,65</t>
+          <t>5,33; 8,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,62</t>
+          <t>3,27; 5,6</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,48</t>
+          <t>1,18; 4,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,07</t>
+          <t>0,7; 3,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,8</t>
+          <t>1,87; 6,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,89</t>
+          <t>0,64; 3,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 12,86</t>
+          <t>6,34; 12,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,5; 7,26</t>
+          <t>3,55; 7,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,34</t>
+          <t>0,15; 1,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,59</t>
+          <t>1,17; 3,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,09; 7,89</t>
+          <t>4,1; 7,66</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 6,15</t>
+          <t>3,15; 6,15</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,8</t>
+          <t>0,94; 4,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,62</t>
+          <t>1,31; 4,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 7,32</t>
+          <t>2,72; 7,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 9,58</t>
+          <t>3,36; 9,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 6,4</t>
+          <t>2,49; 6,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,36; 11,59</t>
+          <t>6,21; 11,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,89; 11,73</t>
+          <t>5,96; 11,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,68</t>
+          <t>1,87; 6,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,39</t>
+          <t>1,85; 4,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,12; 7,44</t>
+          <t>4,13; 7,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,97; 8,68</t>
+          <t>5,03; 8,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,6</t>
+          <t>2,86; 6,37</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 6,93</t>
+          <t>1,87; 7,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,15; 14,6</t>
+          <t>5,91; 14,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,18; 11,52</t>
+          <t>4,55; 11,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,61</t>
+          <t>0,37; 3,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,16; 11,54</t>
+          <t>4,19; 11,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,75; 19,29</t>
+          <t>9,65; 18,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,44; 18,93</t>
+          <t>9,32; 19,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,86</t>
+          <t>1,04; 3,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 8,12</t>
+          <t>3,6; 8,22</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,96; 15,34</t>
+          <t>8,77; 15,39</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,04; 13,6</t>
+          <t>7,99; 13,69</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,94</t>
+          <t>1,05; 2,97</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,45</t>
+          <t>0,36; 3,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,42</t>
+          <t>2,39; 7,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,28; 6,42</t>
+          <t>2,31; 6,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,45</t>
+          <t>1,78; 6,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,08</t>
+          <t>1,76; 6,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,58; 16,53</t>
+          <t>8,61; 16,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,94</t>
+          <t>2,4; 6,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,29</t>
+          <t>1,48; 4,2</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,33</t>
+          <t>1,03; 3,3</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,21; 11,01</t>
+          <t>5,96; 11,12</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,42</t>
+          <t>2,7; 5,45</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,08</t>
+          <t>0,91; 2,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,32</t>
+          <t>1,76; 4,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,75; 6,35</t>
+          <t>2,8; 6,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,29; 7,56</t>
+          <t>3,41; 7,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,1</t>
+          <t>2,17; 5,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,66</t>
+          <t>1,3; 3,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,65; 13,46</t>
+          <t>8,98; 14,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,71; 60,05</t>
+          <t>5,64; 64,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,58</t>
+          <t>1,83; 3,71</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,52</t>
+          <t>1,8; 3,46</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,25; 9,3</t>
+          <t>6,28; 9,4</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,19; 51,05</t>
+          <t>5,16; 46,98</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,07; 6,3</t>
+          <t>2,99; 5,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,6</t>
+          <t>1,88; 4,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,49</t>
+          <t>3,39; 6,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,88</t>
+          <t>0,7; 2,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,2; 7,73</t>
+          <t>4,15; 7,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,05</t>
+          <t>2,55; 5,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,46; 12,97</t>
+          <t>8,6; 13,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,47</t>
+          <t>3,07; 5,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,88; 6,25</t>
+          <t>3,93; 6,47</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,44</t>
+          <t>2,52; 4,47</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,38; 9,21</t>
+          <t>6,41; 9,36</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,75</t>
+          <t>1,66; 3,77</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,4</t>
+          <t>2,25; 3,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,48; 3,66</t>
+          <t>2,55; 3,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,28</t>
+          <t>3,81; 5,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,1</t>
+          <t>2,39; 3,97</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,36</t>
+          <t>3,93; 5,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,28; 5,83</t>
+          <t>4,23; 5,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,01; 12,16</t>
+          <t>9,92; 12,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,34; 26,62</t>
+          <t>4,35; 26,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,25; 4,19</t>
+          <t>3,27; 4,17</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,54; 4,51</t>
+          <t>3,59; 4,53</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,13; 8,52</t>
+          <t>7,25; 8,54</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,74; 16,58</t>
+          <t>3,78; 15,79</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5242; 16695</t>
+          <t>5335; 17656</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5600; 18343</t>
+          <t>5351; 17396</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14582; 32459</t>
+          <t>14366; 34266</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6149; 20743</t>
+          <t>5757; 20990</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9769; 26504</t>
+          <t>9387; 26489</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11177; 27864</t>
+          <t>10202; 27404</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34333; 60094</t>
+          <t>34941; 61683</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3800; 11224</t>
+          <t>4006; 11352</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17650; 38331</t>
+          <t>18575; 38418</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19789; 41341</t>
+          <t>19645; 40635</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53462; 86795</t>
+          <t>53805; 88106</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11748; 28159</t>
+          <t>11149; 27838</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11111; 29593</t>
+          <t>11356; 27127</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7971; 27137</t>
+          <t>7947; 25572</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9474; 26428</t>
+          <t>9545; 25722</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6821; 21161</t>
+          <t>6348; 22006</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19162; 40849</t>
+          <t>18489; 39467</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21098; 43656</t>
+          <t>21493; 42975</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39821; 68473</t>
+          <t>40103; 68425</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22914; 41078</t>
+          <t>23082; 40845</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34801; 61671</t>
+          <t>35317; 62245</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32828; 63022</t>
+          <t>33885; 63298</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54783; 88676</t>
+          <t>54718; 86906</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34080; 58108</t>
+          <t>33752; 57904</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4899</t>
+          <t>0; 4832</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3657; 14503</t>
+          <t>3826; 15161</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2825; 12970</t>
+          <t>2244; 12287</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5731; 21486</t>
+          <t>5916; 20026</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>908; 7731</t>
+          <t>905; 7750</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2884; 13280</t>
+          <t>2189; 13532</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21529; 43260</t>
+          <t>21330; 42204</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12222; 25353</t>
+          <t>12380; 25286</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>970; 8744</t>
+          <t>997; 9518</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8010; 23846</t>
+          <t>7792; 22688</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26795; 51638</t>
+          <t>26851; 50146</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21141; 40881</t>
+          <t>20957; 40918</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2723; 13628</t>
+          <t>3382; 14870</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4921; 17289</t>
+          <t>4908; 17572</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10157; 27071</t>
+          <t>10063; 28475</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10508; 29946</t>
+          <t>10503; 29491</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9098; 23758</t>
+          <t>9263; 24682</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24718; 45094</t>
+          <t>24143; 45527</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22823; 45411</t>
+          <t>23066; 44428</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8745; 27017</t>
+          <t>8889; 28600</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14542; 32076</t>
+          <t>13519; 31221</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31405; 56749</t>
+          <t>31545; 55152</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37668; 65748</t>
+          <t>38121; 65658</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23722; 52043</t>
+          <t>22548; 50209</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4306; 14080</t>
+          <t>3793; 15532</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13085; 31053</t>
+          <t>12564; 31805</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8833; 24330</t>
+          <t>9613; 24663</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>671; 6456</t>
+          <t>667; 6347</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8636; 23960</t>
+          <t>8701; 23569</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21402; 42358</t>
+          <t>21194; 41711</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20638; 41384</t>
+          <t>20370; 42154</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2922; 9998</t>
+          <t>2691; 10161</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15120; 33380</t>
+          <t>14796; 33785</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38745; 66315</t>
+          <t>37893; 66527</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34576; 58463</t>
+          <t>34322; 58825</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4507; 12857</t>
+          <t>4608; 12979</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1035; 9335</t>
+          <t>978; 9208</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4786</t>
+          <t>0; 4709</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6511; 19511</t>
+          <t>6283; 18712</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6142; 17298</t>
+          <t>6222; 17616</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4832; 17948</t>
+          <t>4953; 18017</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4956; 17024</t>
+          <t>4937; 17380</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23421; 45139</t>
+          <t>23520; 45098</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6142; 15274</t>
+          <t>6166; 15440</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8028; 23566</t>
+          <t>8102; 23057</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5869; 18462</t>
+          <t>5702; 18268</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33280; 59023</t>
+          <t>31970; 59604</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13993; 28544</t>
+          <t>14217; 28722</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6176; 18920</t>
+          <t>5595; 18270</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11593; 28662</t>
+          <t>11659; 27459</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18058; 41708</t>
+          <t>18360; 39958</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20529; 47199</t>
+          <t>21309; 44942</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>14397; 32540</t>
+          <t>13872; 31916</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8609; 25389</t>
+          <t>9004; 26178</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>59779; 93058</t>
+          <t>62075; 96755</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>48462; 509972</t>
+          <t>47874; 546999</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>22606; 44916</t>
+          <t>22878; 46453</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23736; 47727</t>
+          <t>24394; 46955</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>84291; 125289</t>
+          <t>84708; 126636</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>76424; 752279</t>
+          <t>76028; 692333</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>22812; 46861</t>
+          <t>22248; 44041</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14853; 35874</t>
+          <t>14633; 37501</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>26602; 50495</t>
+          <t>26422; 50147</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6435; 26724</t>
+          <t>6458; 26633</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>32907; 60562</t>
+          <t>32554; 59707</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20295; 41585</t>
+          <t>20982; 43254</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>69911; 107187</t>
+          <t>71021; 107887</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>21952; 39271</t>
+          <t>22032; 39487</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>59192; 95384</t>
+          <t>60085; 98786</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>38867; 71246</t>
+          <t>40341; 71684</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>102399; 147841</t>
+          <t>102817; 150152</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>28961; 61814</t>
+          <t>27359; 62073</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>72645; 111320</t>
+          <t>73626; 110999</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>84953; 125556</t>
+          <t>87233; 129412</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>130162; 179186</t>
+          <t>129217; 177646</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>88845; 141740</t>
+          <t>82858; 137277</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>129417; 181201</t>
+          <t>132695; 182661</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>152205; 207429</t>
+          <t>150646; 204182</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>354888; 430916</t>
+          <t>351692; 431385</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>161276; 988032</t>
+          <t>161437; 979354</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>216538; 278899</t>
+          <t>217358; 277457</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>247516; 314833</t>
+          <t>250421; 316364</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>495007; 591483</t>
+          <t>502869; 592778</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>268313; 1189282</t>
+          <t>271451; 1132535</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_ner_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,47</t>
+          <t>1,68; 6,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,9</t>
+          <t>1,75; 5,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,89; 11,66</t>
+          <t>4,72; 11,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,74</t>
+          <t>1,69; 5,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,6; 10,16</t>
+          <t>3,66; 9,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 9,54</t>
+          <t>3,59; 9,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,1; 21,37</t>
+          <t>12,42; 21,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,92</t>
+          <t>1,47; 4,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 7,2</t>
+          <t>3,35; 7,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,98</t>
+          <t>3,26; 6,82</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,24; 15,13</t>
+          <t>9,27; 14,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,63</t>
+          <t>1,88; 4,21</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,5</t>
+          <t>2,37; 5,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,06</t>
+          <t>1,57; 5,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,12</t>
+          <t>1,87; 5,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,25</t>
+          <t>1,29; 4,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 7,83</t>
+          <t>3,85; 7,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,1; 8,21</t>
+          <t>4,01; 8,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,67; 13,08</t>
+          <t>7,73; 13,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,48; 7,93</t>
+          <t>4,29; 7,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 6,24</t>
+          <t>3,52; 6,23</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,15</t>
+          <t>3,31; 6,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 8,47</t>
+          <t>5,36; 8,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,6</t>
+          <t>3,25; 5,44</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,68</t>
+          <t>1,13; 4,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,86</t>
+          <t>0,88; 3,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,34</t>
+          <t>1,77; 6,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,31</t>
+          <t>0,27; 2,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,97</t>
+          <t>0,62; 3,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,34; 12,55</t>
+          <t>6,23; 12,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 7,24</t>
+          <t>3,43; 7,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,45</t>
+          <t>0,15; 1,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,41</t>
+          <t>1,18; 3,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,1; 7,66</t>
+          <t>3,95; 7,61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,15</t>
+          <t>3,16; 5,96</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,15</t>
+          <t>0,77; 4,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,7</t>
+          <t>1,31; 4,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,7</t>
+          <t>2,77; 7,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 9,44</t>
+          <t>3,08; 8,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,64</t>
+          <t>2,5; 6,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,21; 11,71</t>
+          <t>6,31; 11,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 11,47</t>
+          <t>5,94; 11,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,01</t>
+          <t>2,72; 6,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,28</t>
+          <t>1,89; 4,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,23</t>
+          <t>3,98; 7,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,03; 8,67</t>
+          <t>5,04; 8,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 6,37</t>
+          <t>3,23; 6,74</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,64</t>
+          <t>2,12; 7,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 14,96</t>
+          <t>6,24; 14,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,55; 11,68</t>
+          <t>4,41; 11,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,55</t>
+          <t>0,35; 2,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 11,35</t>
+          <t>4,19; 11,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,65; 18,99</t>
+          <t>9,82; 19,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,32; 19,28</t>
+          <t>9,61; 18,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,93</t>
+          <t>1,65; 4,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,6; 8,22</t>
+          <t>3,67; 8,26</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,77; 15,39</t>
+          <t>9,04; 15,55</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,99; 13,69</t>
+          <t>7,94; 13,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,97</t>
+          <t>1,25; 3,14</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,4</t>
+          <t>0,38; 3,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,11</t>
+          <t>2,34; 7,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,53</t>
+          <t>2,26; 6,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,48</t>
+          <t>1,72; 6,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 6,21</t>
+          <t>1,79; 6,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,61; 16,51</t>
+          <t>8,5; 16,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,01</t>
+          <t>2,44; 5,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,2</t>
+          <t>1,42; 3,98</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,3</t>
+          <t>1,09; 3,47</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,96; 11,12</t>
+          <t>6,0; 10,95</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,45</t>
+          <t>2,76; 5,27</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,97</t>
+          <t>0,88; 2,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,14</t>
+          <t>1,65; 4,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,8; 6,09</t>
+          <t>2,91; 6,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,41; 7,2</t>
+          <t>3,52; 7,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,0</t>
+          <t>2,25; 5,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,77</t>
+          <t>1,27; 3,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,98; 14,0</t>
+          <t>8,74; 13,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,64; 64,41</t>
+          <t>5,26; 8,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,71</t>
+          <t>1,84; 3,63</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,46</t>
+          <t>1,73; 3,45</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,28; 9,4</t>
+          <t>6,4; 9,56</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,16; 46,98</t>
+          <t>4,73; 7,23</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,99; 5,92</t>
+          <t>2,95; 6,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,81</t>
+          <t>1,87; 4,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,44</t>
+          <t>3,4; 6,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,87</t>
+          <t>1,58; 3,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,15; 7,62</t>
+          <t>4,31; 7,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,25</t>
+          <t>2,46; 5,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,6; 13,06</t>
+          <t>8,58; 12,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,07; 5,5</t>
+          <t>3,11; 5,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,93; 6,47</t>
+          <t>3,88; 6,3</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,52; 4,47</t>
+          <t>2,5; 4,45</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,41; 9,36</t>
+          <t>6,5; 9,29</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,77</t>
+          <t>2,61; 4,24</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,39</t>
+          <t>2,26; 3,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,55; 3,78</t>
+          <t>2,48; 3,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,81; 5,23</t>
+          <t>3,85; 5,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,39; 3,97</t>
+          <t>2,88; 4,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,93; 5,41</t>
+          <t>3,85; 5,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,23; 5,74</t>
+          <t>4,31; 5,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,92; 12,17</t>
+          <t>9,96; 12,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,35; 26,38</t>
+          <t>4,22; 5,48</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,27; 4,17</t>
+          <t>3,24; 4,18</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,59; 4,53</t>
+          <t>3,53; 4,53</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,25; 8,54</t>
+          <t>7,22; 8,59</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,78; 15,79</t>
+          <t>3,75; 4,63</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11361</t>
+          <t>10188</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18265</t>
+          <t>18139</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5335; 17656</t>
+          <t>4590; 17788</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5351; 17396</t>
+          <t>5171; 17464</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14366; 34266</t>
+          <t>13875; 32577</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5757; 20990</t>
+          <t>5375; 17405</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9387; 26489</t>
+          <t>9544; 25625</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10202; 27404</t>
+          <t>10306; 27737</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34941; 61683</t>
+          <t>35851; 60977</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4006; 11352</t>
+          <t>4652; 13394</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18575; 38418</t>
+          <t>17867; 39297</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19645; 40635</t>
+          <t>18952; 39700</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53805; 88106</t>
+          <t>53987; 86954</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11149; 27838</t>
+          <t>11958; 26708</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12802</t>
+          <t>13176</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30841</t>
+          <t>32015</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>43643</t>
+          <t>45191</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11356; 27127</t>
+          <t>11662; 28122</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7947; 25572</t>
+          <t>7938; 27434</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9545; 25722</t>
+          <t>9420; 25702</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6348; 22006</t>
+          <t>6833; 22064</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18489; 39467</t>
+          <t>19422; 40118</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21493; 42975</t>
+          <t>20989; 44275</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40103; 68425</t>
+          <t>40430; 69481</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23082; 40845</t>
+          <t>23440; 42530</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35317; 62245</t>
+          <t>35125; 62107</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33885; 63298</t>
+          <t>34098; 63122</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54718; 86906</t>
+          <t>54984; 88446</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33752; 57904</t>
+          <t>34962; 58585</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11228</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18051</t>
+          <t>18316</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29279</t>
+          <t>28873</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4832</t>
+          <t>0; 4622</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3826; 15161</t>
+          <t>3654; 14643</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2244; 12287</t>
+          <t>2801; 12459</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5916; 20026</t>
+          <t>5595; 20572</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>905; 7750</t>
+          <t>914; 8542</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2189; 13532</t>
+          <t>2126; 13618</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21330; 42204</t>
+          <t>20939; 42047</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12380; 25286</t>
+          <t>12237; 25935</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>997; 9518</t>
+          <t>984; 8779</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7792; 22688</t>
+          <t>7819; 21777</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26851; 50146</t>
+          <t>25883; 49861</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20957; 40918</t>
+          <t>21277; 40094</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17876</t>
+          <t>19590</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16846</t>
+          <t>18437</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>34722</t>
+          <t>38026</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3382; 14870</t>
+          <t>2762; 15120</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4908; 17572</t>
+          <t>4916; 17099</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10063; 28475</t>
+          <t>10246; 27643</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10503; 29491</t>
+          <t>11495; 32133</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9263; 24682</t>
+          <t>9293; 24104</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24143; 45527</t>
+          <t>24535; 45576</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23066; 44428</t>
+          <t>23021; 45740</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8889; 28600</t>
+          <t>11494; 28318</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13519; 31221</t>
+          <t>13781; 32389</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31545; 55152</t>
+          <t>30385; 56137</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38121; 65658</t>
+          <t>38171; 64852</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22548; 50209</t>
+          <t>25689; 53561</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>8772</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3793; 15532</t>
+          <t>4303; 14485</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12564; 31805</t>
+          <t>13277; 30728</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9613; 24663</t>
+          <t>9323; 23421</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>667; 6347</t>
+          <t>723; 6049</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8701; 23569</t>
+          <t>8707; 24700</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21194; 41711</t>
+          <t>21562; 42091</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20370; 42154</t>
+          <t>21008; 40877</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2691; 10161</t>
+          <t>3773; 10705</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14796; 33785</t>
+          <t>15079; 33948</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37893; 66527</t>
+          <t>39082; 67229</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34322; 58825</t>
+          <t>34126; 59601</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4608; 12979</t>
+          <t>5419; 13641</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>10132</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>10016</t>
+          <t>10135</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20618</t>
+          <t>20267</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>978; 9208</t>
+          <t>1025; 8902</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4709</t>
+          <t>0; 5117</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6283; 18712</t>
+          <t>6148; 19995</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6222; 17616</t>
+          <t>6110; 16597</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4953; 18017</t>
+          <t>4777; 17069</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4937; 17380</t>
+          <t>5025; 17587</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23520; 45098</t>
+          <t>23227; 45310</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6166; 15440</t>
+          <t>6426; 15326</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8102; 23057</t>
+          <t>7795; 21824</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5702; 18268</t>
+          <t>6047; 19214</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31970; 59604</t>
+          <t>32155; 58721</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14217; 28722</t>
+          <t>14733; 28161</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30853</t>
+          <t>36845</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>244995</t>
+          <t>51805</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>275848</t>
+          <t>88650</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5595; 18270</t>
+          <t>5428; 18350</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11659; 27459</t>
+          <t>10967; 27529</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18360; 39958</t>
+          <t>19106; 40397</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21309; 44942</t>
+          <t>25355; 52886</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13872; 31916</t>
+          <t>14337; 33256</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9004; 26178</t>
+          <t>8801; 25438</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>62075; 96755</t>
+          <t>60440; 94501</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>47874; 546999</t>
+          <t>40615; 65887</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>22878; 46453</t>
+          <t>23080; 45485</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24394; 46955</t>
+          <t>23515; 46838</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>84708; 126636</t>
+          <t>86271; 128806</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>76028; 692333</t>
+          <t>70627; 107895</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16356</t>
+          <t>19469</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>29926</t>
+          <t>34515</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>46282</t>
+          <t>53984</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>22248; 44041</t>
+          <t>21942; 44966</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14633; 37501</t>
+          <t>14531; 36576</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>26422; 50147</t>
+          <t>26476; 48734</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6458; 26633</t>
+          <t>12617; 30569</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>32554; 59707</t>
+          <t>33760; 61067</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20982; 43254</t>
+          <t>20285; 42456</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>71021; 107887</t>
+          <t>70905; 106716</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>22032; 39487</t>
+          <t>25891; 45530</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>60085; 98786</t>
+          <t>59248; 96262</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>40341; 71684</t>
+          <t>40042; 71390</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>102817; 150152</t>
+          <t>104253; 149042</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>27359; 62073</t>
+          <t>42530; 69082</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>113122</t>
+          <t>122174</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>363717</t>
+          <t>179728</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>476840</t>
+          <t>301902</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>73626; 110999</t>
+          <t>74179; 109749</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>87233; 129412</t>
+          <t>84969; 127591</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>129217; 177646</t>
+          <t>130715; 179509</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>82858; 137277</t>
+          <t>101698; 148500</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>132695; 182661</t>
+          <t>129995; 181669</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>150646; 204182</t>
+          <t>153299; 205236</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>351692; 431385</t>
+          <t>352922; 429414</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>161437; 979354</t>
+          <t>157768; 204755</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>217358; 277457</t>
+          <t>215957; 278037</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>250421; 316364</t>
+          <t>246593; 316238</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>502869; 592778</t>
+          <t>500698; 595868</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>271451; 1132535</t>
+          <t>272941; 336245</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_ner_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
